--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_1706_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_1706_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd04eef0328634635"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R164d5a7bc8c04628"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Piura / Prov: Ayabaca / Dist.: Paimas</x:t>
+          <x:t>Dpto: Piura / Prov: Ayabaca / Dist.: Paimás</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,171 @@
         <x:is>
           <x:t>VALOR (m³/s)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5200</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_1706_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_1706_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R164d5a7bc8c04628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9ec004484d534d33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,621 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
